--- a/Tratamento/src/Dados_limpos/novos/limpo_cobasi_20260515_204859.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_cobasi_20260515_204859.xlsx
@@ -6330,7 +6330,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6540,7 +6540,7 @@
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6754,7 +6754,7 @@
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6964,7 +6964,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_cobasi_20260515_204859.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_cobasi_20260515_204859.xlsx
@@ -6330,7 +6330,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6540,7 +6540,7 @@
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6754,7 +6754,7 @@
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6964,7 +6964,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
